--- a/InputData/indst/PPRiFUfIIaIoE/Pot Perc Red in Fuel Use fr Impr Inst and Integ of Eqpt.xlsx
+++ b/InputData/indst/PPRiFUfIIaIoE/Pot Perc Red in Fuel Use fr Impr Inst and Integ of Eqpt.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="23530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28706"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CodeRepositories\eps-us\InputData\indst\PPRiFUfIIaIoE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F63BBFFB-8C12-499D-B433-EE349EBB73DA}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F63BBFFB-8C12-499D-B433-EE349EBB73DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3540" yWindow="420" windowWidth="23580" windowHeight="15330" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,8 +17,11 @@
     <sheet name="Data" sheetId="2" r:id="rId2"/>
     <sheet name="PPRiFUfIIaIoE" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -26,6 +29,8 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -35,6 +40,9 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="43">
   <si>
+    <t>PPRiFUfIIaIoE Potential Perc Reduction in Fuel Use from Improved Installation and Integration of Eqpt</t>
+  </si>
+  <si>
     <t>Source:</t>
   </si>
   <si>
@@ -50,18 +58,27 @@
     <t>Book page 127, Figure 4-2 (or see link above)</t>
   </si>
   <si>
+    <t>Notes:</t>
+  </si>
+  <si>
+    <t>We exclude agriculture and construction because of their lack of fixed equipment compared to other</t>
+  </si>
+  <si>
+    <t>industries, so this policy likely does not apply very well to them.</t>
+  </si>
+  <si>
     <t>Item</t>
   </si>
   <si>
+    <t>Energy Use (quadrillion BTU/yr)</t>
+  </si>
+  <si>
     <t>2050 business-as-usual</t>
   </si>
   <si>
     <t>Integrative design</t>
   </si>
   <si>
-    <t>Energy Use (quadrillion BTU/yr)</t>
-  </si>
-  <si>
     <t>Percentage Savings in 2050</t>
   </si>
   <si>
@@ -71,10 +88,10 @@
     <t>Percentage Savings in End Year</t>
   </si>
   <si>
-    <t>Notes:</t>
-  </si>
-  <si>
-    <t>PPRiFUfIIaIoE Potential Perc Reduction in Fuel Use from Improved Installation and Integration of Eqpt</t>
+    <t>Unit: dimensionless</t>
+  </si>
+  <si>
+    <t>Pot Perc Red in Fuel Use</t>
   </si>
   <si>
     <t>agriculture and forestry 01T03</t>
@@ -113,6 +130,9 @@
     <t>glass and glass products 231</t>
   </si>
   <si>
+    <t>cement and other nonmetallic minerals 239</t>
+  </si>
+  <si>
     <t>iron and steel 241</t>
   </si>
   <si>
@@ -147,21 +167,6 @@
   </si>
   <si>
     <t>construction 41T43</t>
-  </si>
-  <si>
-    <t>Pot Perc Red in Fuel Use</t>
-  </si>
-  <si>
-    <t>Unit: dimensionless</t>
-  </si>
-  <si>
-    <t>We exclude agriculture and construction because of their lack of fixed equipment compared to other</t>
-  </si>
-  <si>
-    <t>industries, so this policy likely does not apply very well to them.</t>
-  </si>
-  <si>
-    <t>cement and other nonmetallic minerals 239</t>
   </si>
 </sst>
 </file>
@@ -172,7 +177,7 @@
     <numFmt numFmtId="164" formatCode="0.0%"/>
     <numFmt numFmtId="165" formatCode="0.000"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -246,7 +251,7 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -262,16 +267,15 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
-    <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
+    <cellStyle name="Hipervínculo" xfId="2" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Percent" xfId="1" builtinId="5"/>
+    <cellStyle name="Porcentaje" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -287,9 +291,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -327,9 +331,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -362,26 +366,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -414,26 +401,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -608,58 +578,58 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B11"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="41.140625" customWidth="1"/>
     <col min="3" max="3" width="29.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
       <c r="B4" s="2">
         <v>2011</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2">
       <c r="B5" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
       <c r="B6" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
       <c r="B7" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>41</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -674,56 +644,56 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="43.42578125" customWidth="1"/>
     <col min="2" max="2" width="31.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2">
       <c r="A1" s="4" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="B2">
         <v>30.5</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="B3">
         <v>-1.1000000000000001</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="B5" s="5">
         <f>-B3/B2</f>
         <v>3.6065573770491806E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="B6" s="9">
         <v>2050</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2">
       <c r="A7" s="6" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B7" s="7">
         <f>B5*(B6-2010)/(2050-2010)</f>
@@ -741,244 +711,415 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:B26"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="47.7109375" customWidth="1"/>
     <col min="2" max="2" width="25.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="13" t="s">
+    <row r="1" spans="1:2">
+      <c r="A1" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="11" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B3" s="10">
+        <f>Data!B$7</f>
+        <v>3.6065573770491806E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B4" s="10">
+        <f>Data!B$7</f>
+        <v>3.6065573770491806E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>21</v>
+      </c>
+      <c r="B5" s="10">
+        <f>Data!B$7</f>
+        <v>3.6065573770491806E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B6" s="10">
+        <f>Data!B$7</f>
+        <v>3.6065573770491806E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>23</v>
+      </c>
+      <c r="B7" s="10">
+        <f>Data!B$7</f>
+        <v>3.6065573770491806E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
+        <v>24</v>
+      </c>
+      <c r="B8" s="10">
+        <f>Data!B$7</f>
+        <v>3.6065573770491806E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
+        <v>25</v>
+      </c>
+      <c r="B9" s="10">
+        <f>Data!B$7</f>
+        <v>3.6065573770491806E-2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
+        <v>26</v>
+      </c>
+      <c r="B10" s="10">
+        <f>Data!B$7</f>
+        <v>3.6065573770491806E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" t="s">
+        <v>27</v>
+      </c>
+      <c r="B11" s="10">
+        <f>Data!B$7</f>
+        <v>3.6065573770491806E-2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12" t="s">
+        <v>28</v>
+      </c>
+      <c r="B12" s="10">
+        <f>Data!B$7</f>
+        <v>3.6065573770491806E-2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13" t="s">
+        <v>29</v>
+      </c>
+      <c r="B13" s="10">
+        <f>Data!B$7</f>
+        <v>3.6065573770491806E-2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14" t="s">
+        <v>30</v>
+      </c>
+      <c r="B14" s="10">
+        <f>Data!B$7</f>
+        <v>3.6065573770491806E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15" t="s">
+        <v>31</v>
+      </c>
+      <c r="B15" s="10">
+        <f>Data!B$7</f>
+        <v>3.6065573770491806E-2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16" t="s">
+        <v>32</v>
+      </c>
+      <c r="B16" s="10">
+        <f>Data!B$7</f>
+        <v>3.6065573770491806E-2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17" t="s">
+        <v>33</v>
+      </c>
+      <c r="B17" s="10">
+        <f>Data!B$7</f>
+        <v>3.6065573770491806E-2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18" t="s">
+        <v>34</v>
+      </c>
+      <c r="B18" s="10">
+        <f>Data!B$7</f>
+        <v>3.6065573770491806E-2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19" t="s">
+        <v>35</v>
+      </c>
+      <c r="B19" s="10">
+        <f>Data!B$7</f>
+        <v>3.6065573770491806E-2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20" t="s">
+        <v>36</v>
+      </c>
+      <c r="B20" s="10">
+        <f>Data!B$7</f>
+        <v>3.6065573770491806E-2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21" t="s">
+        <v>37</v>
+      </c>
+      <c r="B21" s="10">
+        <f>Data!B$7</f>
+        <v>3.6065573770491806E-2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="A22" t="s">
+        <v>38</v>
+      </c>
+      <c r="B22" s="10">
+        <f>Data!B$7</f>
+        <v>3.6065573770491806E-2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
+      <c r="A23" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="12" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B2" s="11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B3" s="10">
-        <f>Data!B$7</f>
-        <v>3.6065573770491806E-2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B4" s="10">
-        <f>Data!B$7</f>
-        <v>3.6065573770491806E-2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>17</v>
-      </c>
-      <c r="B5" s="10">
-        <f>Data!B$7</f>
-        <v>3.6065573770491806E-2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>18</v>
-      </c>
-      <c r="B6" s="10">
-        <f>Data!B$7</f>
-        <v>3.6065573770491806E-2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>19</v>
-      </c>
-      <c r="B7" s="10">
-        <f>Data!B$7</f>
-        <v>3.6065573770491806E-2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>20</v>
-      </c>
-      <c r="B8" s="10">
-        <f>Data!B$7</f>
-        <v>3.6065573770491806E-2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>21</v>
-      </c>
-      <c r="B9" s="10">
-        <f>Data!B$7</f>
-        <v>3.6065573770491806E-2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>22</v>
-      </c>
-      <c r="B10" s="10">
-        <f>Data!B$7</f>
-        <v>3.6065573770491806E-2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>23</v>
-      </c>
-      <c r="B11" s="10">
-        <f>Data!B$7</f>
-        <v>3.6065573770491806E-2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>24</v>
-      </c>
-      <c r="B12" s="10">
-        <f>Data!B$7</f>
-        <v>3.6065573770491806E-2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>25</v>
-      </c>
-      <c r="B13" s="10">
-        <f>Data!B$7</f>
-        <v>3.6065573770491806E-2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
+      <c r="B23" s="10">
+        <f>Data!B$7</f>
+        <v>3.6065573770491806E-2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
+      <c r="A24" t="s">
+        <v>40</v>
+      </c>
+      <c r="B24" s="10">
+        <f>Data!B$7</f>
+        <v>3.6065573770491806E-2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
+      <c r="A25" t="s">
+        <v>41</v>
+      </c>
+      <c r="B25" s="10">
+        <f>Data!B$7</f>
+        <v>3.6065573770491806E-2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2">
+      <c r="A26" t="s">
         <v>42</v>
       </c>
-      <c r="B14" s="10">
-        <f>Data!B$7</f>
-        <v>3.6065573770491806E-2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>26</v>
-      </c>
-      <c r="B15" s="10">
-        <f>Data!B$7</f>
-        <v>3.6065573770491806E-2</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>27</v>
-      </c>
-      <c r="B16" s="10">
-        <f>Data!B$7</f>
-        <v>3.6065573770491806E-2</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>28</v>
-      </c>
-      <c r="B17" s="10">
-        <f>Data!B$7</f>
-        <v>3.6065573770491806E-2</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>29</v>
-      </c>
-      <c r="B18" s="10">
-        <f>Data!B$7</f>
-        <v>3.6065573770491806E-2</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>30</v>
-      </c>
-      <c r="B19" s="10">
-        <f>Data!B$7</f>
-        <v>3.6065573770491806E-2</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>31</v>
-      </c>
-      <c r="B20" s="10">
-        <f>Data!B$7</f>
-        <v>3.6065573770491806E-2</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>32</v>
-      </c>
-      <c r="B21" s="10">
-        <f>Data!B$7</f>
-        <v>3.6065573770491806E-2</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>33</v>
-      </c>
-      <c r="B22" s="10">
-        <f>Data!B$7</f>
-        <v>3.6065573770491806E-2</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>34</v>
-      </c>
-      <c r="B23" s="10">
-        <f>Data!B$7</f>
-        <v>3.6065573770491806E-2</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>35</v>
-      </c>
-      <c r="B24" s="10">
-        <f>Data!B$7</f>
-        <v>3.6065573770491806E-2</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>36</v>
-      </c>
-      <c r="B25" s="10">
-        <f>Data!B$7</f>
-        <v>3.6065573770491806E-2</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>37</v>
-      </c>
-      <c r="B26" s="11">
+      <c r="B26">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009A9DAB439B36DB4795F39C4E722C7BC4" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="44674c89fa9bc5e97a878a6680c46188">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="79748b23-d81a-423e-9112-21109dc864e6" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="447839a363ea5a12024b5bf1ab53ed90" ns2:_="">
+    <xsd:import namespace="79748b23-d81a-423e-9112-21109dc864e6"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="79748b23-d81a-423e-9112-21109dc864e6" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="11" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A1725439-2EB2-4AEF-AA73-C4792D0E6E12}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9406FD02-1668-407C-B73A-B5816640BA26}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AA58B0D0-251A-4AAC-A50E-89862D4541F2}"/>
 </file>